--- a/translationtoolservice/src/main/resources/config/通用词条翻译模板_common.xlsx
+++ b/translationtoolservice/src/main/resources/config/通用词条翻译模板_common.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>通用反义词条导入模板</t>
   </si>
@@ -44,13 +44,10 @@
     <t>词条标签</t>
   </si>
   <si>
-    <t>relay_start</t>
+    <t>中文释义</t>
   </si>
   <si>
-    <t>启动</t>
-  </si>
-  <si>
-    <t>Start</t>
+    <t>英文释义</t>
   </si>
 </sst>
 </file>
@@ -535,7 +532,7 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1229,22 +1226,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <dimension ref="A1:F38"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="25.7166666666667" customWidth="1"/>
     <col min="4" max="4" width="17.875" customWidth="1"/>
+    <col min="5" max="5" width="18.375" customWidth="1"/>
+    <col min="6" max="6" width="19.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" spans="1:4">
+    <row r="1" ht="20.25" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" ht="37.5" spans="1:4">
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" ht="37.5" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1257,17 +1258,17 @@
       <c r="D2" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+      <c r="E2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="3"/>
@@ -1446,7 +1447,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
